--- a/Module_C_Labs_SOLVED.xlsx
+++ b/Module_C_Labs_SOLVED.xlsx
@@ -5734,7 +5734,7 @@
       </c>
       <c r="C7" s="38" t="inlineStr">
         <is>
-          <t>ניקוי תיאור: רווח קשיח, סימני כיווניות שהבנק משאיר, ורווחים כפולים</t>
+          <t>ניקוי תיאור: תווים נסתרים שהבנק משאיר, ורווחים כפולים</t>
         </is>
       </c>
       <c r="D7" s="39" t="inlineStr">
